--- a/hardware/1v5/Project Outputs for LimePSB-RPCM_1v5/BOM/LimePSB-RPCM_1v5_BOMr0_(Default).xlsx
+++ b/hardware/1v5/Project Outputs for LimePSB-RPCM_1v5/BOM/LimePSB-RPCM_1v5_BOMr0_(Default).xlsx
@@ -2146,7 +2146,7 @@
     <t xml:space="preserve">1k, 1%</t>
   </si>
   <si>
-    <t xml:space="preserve">R33, R41, R74, R78, R193, R200, R319, R332, R338</t>
+    <t xml:space="preserve">R33, R44, R74, R78, R193, R200, R319, R332, R338</t>
   </si>
   <si>
     <t xml:space="preserve">RMCF0402FT1K00</t>
